--- a/Rekap_Masukan_Perbaikan_DNP_Monitor (1) (5).xlsx
+++ b/Rekap_Masukan_Perbaikan_DNP_Monitor (1) (5).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download Backup\Lovable\dnp-monitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AFE64D-99C1-4F53-9083-F122F453A928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE20C87-C616-4645-AA23-C41C769E27CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="326">
   <si>
     <t>REKAP STATUS PEMBARUAN &amp; TRACKING PERBAIKAN — DNP MONITOR</t>
   </si>
@@ -1341,7 +1341,7 @@
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1452,24 +1452,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFD4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFAFAFA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1514,6 +1496,42 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FFFAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor rgb="FFFAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor rgb="FFCCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FFCCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -1574,7 +1592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1664,9 +1682,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1685,11 +1700,6 @@
     <xf numFmtId="0" fontId="24" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1752,22 +1762,22 @@
     <xf numFmtId="0" fontId="21" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1784,6 +1794,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1808,10 +1820,40 @@
     <xf numFmtId="0" fontId="21" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2433,10 +2475,10 @@
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="75" t="s">
         <v>144</v>
       </c>
-      <c r="C10" s="44"/>
+      <c r="C10" s="76"/>
     </row>
     <row r="11" spans="2:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
@@ -2479,10 +2521,10 @@
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="44"/>
+      <c r="C17" s="76"/>
     </row>
     <row r="18" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
@@ -2517,10 +2559,10 @@
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="C23" s="44"/>
+      <c r="C23" s="76"/>
     </row>
     <row r="24" spans="2:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
@@ -2579,22 +2621,22 @@
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>3</v>
       </c>
@@ -2611,7 +2653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B6" s="25">
         <f>COUNTA(A10:A41)</f>
         <v>32</v>
@@ -2633,7 +2675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
         <v>8</v>
       </c>
@@ -2656,148 +2698,145 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="62" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="57">
+    <row r="10" spans="1:7" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="49">
         <v>1</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="60" t="s">
+      <c r="E10" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="61" t="s">
+      <c r="F10" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="60" t="s">
+      <c r="G10" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="62" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="50" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45">
+    </row>
+    <row r="11" spans="1:7" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="41">
         <v>2</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="44" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="50" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53">
+    <row r="12" spans="1:7" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="49">
         <v>3</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="49" t="s">
+      <c r="F12" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="56" t="s">
+      <c r="G12" s="52" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="50" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45">
+    <row r="13" spans="1:7" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="41">
         <v>4</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D13" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="48" t="s">
+      <c r="E13" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="49" t="s">
+      <c r="F13" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="50" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="53">
+    <row r="14" spans="1:7" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="49">
         <v>5</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="55" t="s">
+      <c r="D14" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="52" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36">
+    <row r="15" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="35">
         <v>6</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="39" t="s">
+      <c r="G15" s="38" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="31">
         <v>7</v>
       </c>
@@ -2813,7 +2852,7 @@
       <c r="E16" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="39" t="s">
         <v>6</v>
       </c>
       <c r="G16" s="34" t="s">
@@ -2821,25 +2860,25 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36">
+      <c r="A17" s="35">
         <v>8</v>
       </c>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="38" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2859,569 +2898,566 @@
       <c r="E18" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="40" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="34" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="62" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="63">
+    <row r="19" spans="1:8" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="41">
         <v>10</v>
       </c>
-      <c r="B19" s="64" t="s">
+      <c r="B19" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="65" t="s">
+      <c r="D19" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="66" t="s">
+      <c r="E19" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="61" t="s">
+      <c r="F19" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="66" t="s">
+      <c r="G19" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="62" t="s">
+    </row>
+    <row r="20" spans="1:8" s="58" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="53">
+        <v>11</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="41">
+        <v>12</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="46" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="74" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="77">
+        <v>13</v>
+      </c>
+      <c r="B22" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" s="80" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="74" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="41">
+        <v>14</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="46" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="72" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67">
-        <v>11</v>
-      </c>
-      <c r="B20" s="68" t="s">
+    <row r="24" spans="1:8" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="49">
+        <v>15</v>
+      </c>
+      <c r="B24" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="67" t="s">
+      <c r="C24" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="52" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="46" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="41">
+        <v>16</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="46" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="58" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="53">
+        <v>17</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" s="56" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="64" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="59">
+        <v>18</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="64" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="64" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="65">
+        <v>19</v>
+      </c>
+      <c r="B28" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="67" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" s="64" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="74" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="69">
+        <v>20</v>
+      </c>
+      <c r="B29" s="70" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="72" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="74" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="49">
         <v>21</v>
       </c>
-      <c r="D20" s="69" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="71" t="s">
+      <c r="B30" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="70" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="72" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="78" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="73">
-        <v>12</v>
-      </c>
-      <c r="B21" s="74" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="75" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="76" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="77" t="s">
+      <c r="G30" s="52" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="58" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="81">
+        <v>22</v>
+      </c>
+      <c r="B31" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="81" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="83" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" s="78" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" s="62" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="57">
-        <v>13</v>
-      </c>
-      <c r="B22" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="59" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="60" t="s">
-        <v>64</v>
-      </c>
-      <c r="F22" s="61" t="s">
+      <c r="G31" s="84" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="58" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="53">
+        <v>23</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="D32" s="55" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="H22" s="62" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="62" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="63">
-        <v>14</v>
-      </c>
-      <c r="B23" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="E23" s="66" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="61" t="s">
+      <c r="G32" s="56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="58" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="81">
+        <v>24</v>
+      </c>
+      <c r="B33" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="E33" s="84" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="66" t="s">
-        <v>69</v>
-      </c>
-      <c r="H23" s="62" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="62" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="57">
-        <v>15</v>
-      </c>
-      <c r="B24" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="57" t="s">
+      <c r="G33" s="84" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="58" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="53">
+        <v>25</v>
+      </c>
+      <c r="B34" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="90" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="85">
+        <v>26</v>
+      </c>
+      <c r="B35" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="85" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="88" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="88" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="90" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="91">
+        <v>27</v>
+      </c>
+      <c r="B36" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="93" t="s">
+        <v>113</v>
+      </c>
+      <c r="E36" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F36" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="94" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="90" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="85">
+        <v>28</v>
+      </c>
+      <c r="B37" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="85" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="87" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="88" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="46" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="49">
+        <v>29</v>
+      </c>
+      <c r="B38" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="95" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="90" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="85">
+        <v>30</v>
+      </c>
+      <c r="B39" s="86" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="85" t="s">
+        <v>124</v>
+      </c>
+      <c r="D39" s="87" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" s="88" t="s">
+        <v>126</v>
+      </c>
+      <c r="F39" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="88" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="90" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="91">
+        <v>31</v>
+      </c>
+      <c r="B40" s="92" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="93" t="s">
+        <v>128</v>
+      </c>
+      <c r="E40" s="94" t="s">
+        <v>129</v>
+      </c>
+      <c r="F40" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="94" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="90" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="85">
         <v>32</v>
       </c>
-      <c r="D24" s="59" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>71</v>
-      </c>
-      <c r="F24" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="62" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="78" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="73">
-        <v>16</v>
-      </c>
-      <c r="B25" s="74" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="78" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="72" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67">
-        <v>17</v>
-      </c>
-      <c r="B26" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="70" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="78" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="73">
-        <v>18</v>
-      </c>
-      <c r="B27" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="75" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="78" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="78" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="79">
-        <v>19</v>
-      </c>
-      <c r="B28" s="80" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="79" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="82" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="82" t="s">
-        <v>86</v>
-      </c>
-      <c r="H28" s="78" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="88" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="83">
-        <v>20</v>
-      </c>
-      <c r="B29" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="85" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="86" t="s">
-        <v>89</v>
-      </c>
-      <c r="F29" s="87" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="86" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="88" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31">
-        <v>21</v>
-      </c>
-      <c r="B30" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="E30" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G30" s="34" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="36">
-        <v>22</v>
-      </c>
-      <c r="B31" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="F31" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="31">
-        <v>23</v>
-      </c>
-      <c r="B32" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="F32" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="36">
-        <v>24</v>
-      </c>
-      <c r="B33" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="F33" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="31">
-        <v>25</v>
-      </c>
-      <c r="B34" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G34" s="34" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="36">
-        <v>26</v>
-      </c>
-      <c r="B35" s="37" t="s">
+      <c r="B41" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E35" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="F35" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="39" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="31">
-        <v>27</v>
-      </c>
-      <c r="B36" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" s="31" t="s">
+      <c r="C41" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" s="34" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="36">
-        <v>28</v>
-      </c>
-      <c r="B37" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="E37" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="F37" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" s="39" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="31">
-        <v>29</v>
-      </c>
-      <c r="B38" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="F38" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="34" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="36">
-        <v>30</v>
-      </c>
-      <c r="B39" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" s="39" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="31">
-        <v>31</v>
-      </c>
-      <c r="B40" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="E40" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="F40" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G40" s="34" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="36">
-        <v>32</v>
-      </c>
-      <c r="B41" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="38" t="s">
+      <c r="D41" s="87" t="s">
         <v>131</v>
       </c>
-      <c r="E41" s="39" t="s">
+      <c r="E41" s="88" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="41" t="s">
+      <c r="F41" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="G41" s="39" t="s">
+      <c r="G41" s="88" t="s">
         <v>133</v>
       </c>
     </row>
@@ -3708,105 +3744,105 @@
       <c r="J10" s="8"/>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" s="50" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="51">
+    <row r="11" spans="1:11" s="46" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="47">
         <v>10</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="47" t="s">
         <v>220</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="48" t="s">
         <v>221</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52" t="s">
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="52"/>
-    </row>
-    <row r="12" spans="1:11" s="50" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="51">
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="48"/>
+    </row>
+    <row r="12" spans="1:11" s="46" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="47">
         <v>11</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="47" t="s">
         <v>224</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52" t="s">
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="52"/>
-    </row>
-    <row r="13" spans="1:11" s="50" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="51">
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="48"/>
+    </row>
+    <row r="13" spans="1:11" s="46" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="47">
         <v>12</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="48" t="s">
         <v>231</v>
       </c>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52" t="s">
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="52"/>
-    </row>
-    <row r="14" spans="1:11" s="50" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="51">
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="48"/>
+    </row>
+    <row r="14" spans="1:11" s="46" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="47">
         <v>13</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="48" t="s">
         <v>234</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="E14" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52" t="s">
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="52"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="48"/>
     </row>
     <row r="15" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
